--- a/tame_output/ON/bt/strategyON_20240405.xlsx
+++ b/tame_output/ON/bt/strategyON_20240405.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-496.0%</t>
+          <t>-495.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -45803,10 +45803,10 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.343882725567093</v>
+        <v>-3.342368489415919</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.741094468928983</v>
+        <v>1.741700163389453</v>
       </c>
       <c r="F1924" t="n">
         <v>0.3397452342405004</v>

--- a/tame_output/ON/bt/strategyON_20240405.xlsx
+++ b/tame_output/ON/bt/strategyON_20240405.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>113.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,22 +1002,22 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>496.2%</t>
+          <t>495.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-495.8%</t>
+          <t>-520.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-202.1%</t>
+          <t>-212.0%</t>
         </is>
       </c>
     </row>
@@ -45803,10 +45803,10 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.342368489415919</v>
+        <v>-3.591630754073714</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.741700163389453</v>
+        <v>1.641995257526335</v>
       </c>
       <c r="F1924" t="n">
         <v>0.3397452342405004</v>

--- a/tame_output/ON/bt/strategyON_20240405.xlsx
+++ b/tame_output/ON/bt/strategyON_20240405.xlsx
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317622</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.728574354425329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353075</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.421166422609705</v>
+        <v>3.421166422609703</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>

--- a/tame_output/ON/bt/strategyON_20240405.xlsx
+++ b/tame_output/ON/bt/strategyON_20240405.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-30.6%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.3%</t>
+          <t>132.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>495.5%</t>
+          <t>495.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-117.7%</t>
+          <t>-165.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1924"/>
+  <dimension ref="A1:G1925"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309427</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970908</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097826</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317622</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737176</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341319</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425329</v>
+        <v>3.728574354425331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353075</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.421166422609703</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
@@ -45813,6 +45813,29 @@
       </c>
       <c r="G1924" t="n">
         <v>3.282851124013868</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="2" t="n">
+        <v>45387</v>
+      </c>
+      <c r="B1925" t="n">
+        <v>3.433653674620584</v>
+      </c>
+      <c r="C1925" t="n">
+        <v>2.810424437558775</v>
+      </c>
+      <c r="D1925" t="n">
+        <v>-3.591630754073714</v>
+      </c>
+      <c r="E1925" t="n">
+        <v>1.641995257526335</v>
+      </c>
+      <c r="F1925" t="n">
+        <v>0.3397452342405004</v>
+      </c>
+      <c r="G1925" t="n">
+        <v>2.803488234545143</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240405.xlsx
+++ b/tame_output/ON/bt/strategyON_20240405.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>49.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,85 +791,85 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>113.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.2%</t>
+          <t>131.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>495.7%</t>
+          <t>500.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-520.7%</t>
+          <t>-518.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>581.4%</t>
+          <t>-3703.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-212.0%</t>
+          <t>-211.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.1%</t>
+          <t>-161.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-190.0%</t>
+          <t>-186.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.7%</t>
+          <t>-133.1%</t>
         </is>
       </c>
     </row>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.426778384575448</v>
+        <v>-5.401762403767835</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9463566827791547</v>
+        <v>0.9563630751022001</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-0.8923256160783768</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.582029091276056</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.424351320046729</v>
+        <v>-5.399335339239117</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9465820235964735</v>
+        <v>0.9565884159195188</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9246304134785115</v>
+        <v>-0.8926583978855285</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.561900727841806</v>
+        <v>2.581083937197596</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.832940097227407</v>
+        <v>-5.807924116419795</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7819080567389616</v>
+        <v>0.7919144490620065</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.301247175066207</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.315509005548158</v>
+        <v>2.334692214903948</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.245922581368501</v>
+        <v>-6.220906600560888</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6119004955539844</v>
+        <v>0.6219068878770297</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.301247175066207</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.310694438019619</v>
+        <v>2.329877647375409</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.662314455655499</v>
+        <v>-6.637298474847886</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4433377964480627</v>
+        <v>0.453344188771108</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.301247175066207</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.308688488628496</v>
+        <v>2.327871697984286</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.038991466185343</v>
+        <v>-7.01397548537773</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3029256829048039</v>
+        <v>0.3129320752278493</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.301247175066207</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.318947179297175</v>
+        <v>2.338130388652965</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.052706330510454</v>
+        <v>-7.027690349702842</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2935393023204549</v>
+        <v>0.3035456946434998</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.301247175066207</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.31504674444287</v>
+        <v>2.33422995379866</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.365531129755434</v>
+        <v>-7.340515148947821</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.166814302677464</v>
+        <v>0.1768206950005089</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.301247175066207</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.313451664497871</v>
+        <v>2.332634873853661</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.370344168220771</v>
+        <v>-7.345328187413158</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1686680632205371</v>
+        <v>0.1786744555435824</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.302793809768993</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.316302659605408</v>
+        <v>2.335485868961197</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.803693276331007</v>
+        <v>-7.778677295523394</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.008697884557960389</v>
+        <v>0.001308507765084954</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.302793809768993</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.312276355071005</v>
+        <v>2.331459564426795</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.186694665073638</v>
+        <v>-8.161678684266025</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1620005413765968</v>
+        <v>-0.1519941490535519</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.302793809768993</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.312174253749421</v>
+        <v>2.331357463105211</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.561679991244915</v>
+        <v>-8.536664010437303</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.3094231558736777</v>
+        <v>-0.2994167635506324</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.67777913594027</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.089754574018084</v>
+        <v>2.108937783373874</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.921210313748917</v>
+        <v>-8.896194332941304</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.4478849815772281</v>
+        <v>-0.4378785892541828</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.67777913594027</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.095104877316134</v>
+        <v>2.114288086671924</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.24761034241393</v>
+        <v>-9.222594361606317</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5705289730860557</v>
+        <v>-0.5605225807630108</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.036151180198266</v>
+        <v>-2.004179164605283</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.907180880074304</v>
+        <v>1.926364089430094</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.24113419562037</v>
+        <v>-9.216118214812758</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5648967637468632</v>
+        <v>-0.5548903714238178</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.029675033404706</v>
+        <v>-1.997703017811723</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.914108318772209</v>
+        <v>1.933291528127999</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.23744327066396</v>
+        <v>-9.212427289856347</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.5634203937642988</v>
+        <v>-0.5534140014412539</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.029675033404706</v>
+        <v>-1.997703017811723</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.914108318772209</v>
+        <v>1.933291528127999</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.441701445993823</v>
+        <v>-9.416685465186211</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.6396104667776017</v>
+        <v>-0.6296040744545568</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.157313978018695</v>
+        <v>-2.125341962425712</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.843038149122458</v>
+        <v>1.862221358478248</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.602340472482188</v>
+        <v>-9.577324491674576</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.6993835228885117</v>
+        <v>-0.6893771305654668</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.272047451021091</v>
+        <v>-2.240075435428108</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.778680619805457</v>
+        <v>1.797863829161247</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.528870640814739</v>
+        <v>-9.503854660007127</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6546238887281111</v>
+        <v>-0.6446174964050662</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.198577619353642</v>
+        <v>-2.166605603760659</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.838134220299347</v>
+        <v>1.857317429655137</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.703995058201283</v>
+        <v>-9.67897907739367</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7101184349352119</v>
+        <v>-0.7001120426121665</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.341730021147203</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.747614790614937</v>
+        <v>1.766797999970727</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.938447152215772</v>
+        <v>-9.91343117140816</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8111184374426035</v>
+        <v>-0.8011120451195586</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.341730021147203</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.740395625713341</v>
+        <v>1.759578835069131</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.22625099675301</v>
+        <v>-10.2012350159454</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9329121660314752</v>
+        <v>-0.9229057737084303</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.661505881277424</v>
+        <v>-2.629533865684441</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.561041128217022</v>
+        <v>1.580224337572812</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.45607544391684</v>
+        <v>-10.43105946310922</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.023726155058449</v>
+        <v>-1.013719762735404</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.824153418347585</v>
+        <v>-2.792181402754602</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.464568395813482</v>
+        <v>1.483751605169272</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.6881043636531</v>
+        <v>-10.66308838284549</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.113843994323839</v>
+        <v>-1.103837602000794</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.854194099943025</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.430054506129543</v>
+        <v>1.449237715485333</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63608884968428</v>
+        <v>-10.61107286887667</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.089047453049913</v>
+        <v>-1.079041060726868</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.854194099943025</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.434044841815944</v>
+        <v>1.453228051171734</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.7777606914084</v>
+        <v>-10.75274471060079</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.147191416638303</v>
+        <v>-1.137185024315258</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.854194099943025</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.432569614917202</v>
+        <v>1.451752824272992</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.87666743186768</v>
+        <v>-10.85165145106007</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.17170070265714</v>
+        <v>-1.161694310334096</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.985072855995284</v>
+        <v>-2.9531008404023</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.388278980806509</v>
+        <v>1.407462190162299</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.67751532463058</v>
+        <v>-10.65249934382297</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.105090993408984</v>
+        <v>-1.095084601085939</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.81975033004547</v>
+        <v>-2.787778314452487</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.474421362729714</v>
+        <v>1.493604572085504</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.45167017191117</v>
+        <v>-10.42665419110356</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.005173859285012</v>
+        <v>-0.9951674669619659</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.777823654458307</v>
+        <v>-2.745851638865323</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.509156441118221</v>
+        <v>1.528339650474011</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.16539535958848</v>
+        <v>-10.14037937878086</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8895247897998746</v>
+        <v>-0.8795183974768297</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.777823654458307</v>
+        <v>-2.745851638865323</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.51029558567428</v>
+        <v>1.52947879503007</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.21829064763276</v>
+        <v>-10.19327466682515</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9080491308554812</v>
+        <v>-0.8980427385324363</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.772868308369861</v>
+        <v>-2.740896292776877</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.515902567489455</v>
+        <v>1.535085776845245</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.934381916704014</v>
+        <v>-9.909365935896401</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.7887519342453455</v>
+        <v>-0.7787455419223002</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.772868308369861</v>
+        <v>-2.740896292776877</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.521636271728092</v>
+        <v>1.540819481083882</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.687394666511063</v>
+        <v>-9.66237868570345</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6996942965620301</v>
+        <v>-0.6896879042389847</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.493909042583925</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.660091359449998</v>
+        <v>1.679274568805788</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.423557799306993</v>
+        <v>-9.39854181849938</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.6040430309933096</v>
+        <v>-0.5940366386702647</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.493909042583925</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.65020787813709</v>
+        <v>1.66939108749288</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.156315998438595</v>
+        <v>-9.131300017630982</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4989808711453243</v>
+        <v>-0.488974478822279</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.493909042583925</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.648373317637716</v>
+        <v>1.667556526993506</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.88050683503811</v>
+        <v>-8.855490854230498</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3889575207585909</v>
+        <v>-0.378951128435546</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.436861749898175</v>
+        <v>-2.404889734305192</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.701484587631496</v>
+        <v>1.720667796987286</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.611439247271131</v>
+        <v>-8.586423266463518</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2806619795063057</v>
+        <v>-0.2706555871832603</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.167794162131196</v>
+        <v>-2.135822146538212</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.863593646437177</v>
+        <v>1.882776855792967</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.347379308948334</v>
+        <v>-8.322363328140721</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.188298320338939</v>
+        <v>-0.1782919280158941</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.9037342238084</v>
+        <v>-1.871762208215416</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.008769293269102</v>
+        <v>2.027952502624892</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.640299685443495</v>
+        <v>-7.615283704635883</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.09174649540269542</v>
+        <v>0.1017528877257403</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.9037342238084</v>
+        <v>-1.871762208215416</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.005982259608801</v>
+        <v>2.025165468964591</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.390658655457544</v>
+        <v>-7.365642674649931</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1919465312849176</v>
+        <v>0.2019529236079625</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.654093193822448</v>
+        <v>-1.622121178229464</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.156110501488214</v>
+        <v>2.175293710844004</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.136116756116468</v>
+        <v>-7.111100775308856</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2931301122421046</v>
+        <v>0.3031365045651495</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.399551294481372</v>
+        <v>-1.367579278888389</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.308202462313616</v>
+        <v>2.327385671669406</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.90263553388687</v>
+        <v>-6.877619553079257</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3944470299717961</v>
+        <v>0.4044534222948415</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.166070072251774</v>
+        <v>-1.13409805665879</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.456215624489228</v>
+        <v>2.475398833845018</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.722927003742997</v>
+        <v>-6.697911022935385</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4634382317163861</v>
+        <v>0.4734446240394314</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.108898568089078</v>
+        <v>-1.076926552496094</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.487626316673886</v>
+        <v>2.506809526029676</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.590651530112111</v>
+        <v>-6.565635549304498</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5117159079157676</v>
+        <v>0.5217223002388129</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9766230944581911</v>
+        <v>-0.9446510788652076</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.562359087599445</v>
+        <v>2.581542296955235</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.400051855438958</v>
+        <v>-6.375035874631346</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5907708384726655</v>
+        <v>0.6007772307957104</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7860234197850382</v>
+        <v>-0.7540514041920547</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.679533953090973</v>
+        <v>2.698717162446764</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.151052056755377</v>
+        <v>-6.126036075947765</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.7032770991697568</v>
+        <v>0.7132834914928017</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7860234197850382</v>
+        <v>-0.7540514041920547</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.692440294314632</v>
+        <v>2.711623503670422</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.256642046528482</v>
+        <v>-6.231626065720869</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5330651736612961</v>
+        <v>0.5430715659843415</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8916134095581425</v>
+        <v>-0.859641393965159</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.501110370851551</v>
+        <v>2.520293580207341</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.275376948647079</v>
+        <v>-6.250360967839466</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5741155546909438</v>
+        <v>0.5841219470139887</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8916134095581425</v>
+        <v>-0.859641393965159</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.549654712728637</v>
+        <v>2.568837922084428</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.998638773976266</v>
+        <v>-5.973622793168653</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.6881898365452637</v>
+        <v>0.6981962288683086</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.7097967484482167</v>
+        <v>-0.6778247328552333</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.662123721380588</v>
+        <v>2.681306930736377</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.871746367541196</v>
+        <v>-5.846730386733583</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.7302328128658138</v>
+        <v>0.7402392051888587</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5509323264201633</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.729545178988151</v>
+        <v>2.748728388343941</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.684158859631269</v>
+        <v>-5.659142878823657</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.7983072039346908</v>
+        <v>0.8083135962577361</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5509323264201633</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.722584566893058</v>
+        <v>2.741767776248848</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.442010466177411</v>
+        <v>-5.416994485369798</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.9096289156973771</v>
+        <v>0.9196353080204225</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5509323264201633</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.737046921274201</v>
+        <v>2.756230130629991</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.378781094409063</v>
+        <v>-5.35376511360145</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.9294527848639116</v>
+        <v>0.9394591771869569</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5509323264201633</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.731579041733396</v>
+        <v>2.750762251089186</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.192293402032057</v>
+        <v>-5.167277421224444</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.001545955825291</v>
+        <v>1.011552348148336</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3964166496361405</v>
+        <v>-0.3644446340431571</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.840969751170177</v>
+        <v>2.860152960525967</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.171144203128613</v>
+        <v>-5.146128222321001</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.017706613623994</v>
+        <v>1.027713005947039</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3752674507326972</v>
+        <v>-0.3432954351397137</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.861360248749568</v>
+        <v>2.880543458105358</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.927378761145169</v>
+        <v>-4.902362780337556</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.110993498764422</v>
+        <v>1.120999891087467</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3752674507326972</v>
+        <v>-0.3432954351397137</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.857140957096619</v>
+        <v>2.87632416645241</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.663350693951909</v>
+        <v>-4.638334713144296</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.218729039561742</v>
+        <v>1.228735431884788</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.1414300363237602</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.980384510306207</v>
+        <v>2.999567719661997</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.413500300002834</v>
+        <v>-4.388484319195221</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.311411272125075</v>
+        <v>1.321417664448119</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.1414300363237602</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.97312658528991</v>
+        <v>2.9923097946457</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.109932810998855</v>
+        <v>-4.084916830191243</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.436437391247315</v>
+        <v>1.44644378357036</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.1414300363237602</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.976725708810558</v>
+        <v>2.995908918166348</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.036452902146841</v>
+        <v>-4.011436921339229</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.479156860842674</v>
+        <v>1.489163253165719</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.09992214306472924</v>
+        <v>-0.06795012747174578</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.034141160176321</v>
+        <v>3.053324369532111</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.811419902478018</v>
+        <v>-3.786403921670406</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.5681905383265</v>
+        <v>1.578196930649545</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1251108566040936</v>
+        <v>0.1570828721970771</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.168181437593911</v>
+        <v>3.187364646949701</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.596785524841612</v>
+        <v>-3.571769544033999</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.65873909043538</v>
+        <v>1.668745482758425</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3397452342405004</v>
+        <v>0.3717172498334839</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.301656865230072</v>
+        <v>3.320840074585863</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.591630754073714</v>
+        <v>-3.566614773266101</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.641995257526335</v>
+        <v>1.65200164984938</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3397452342405004</v>
+        <v>0.3717172498334839</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.282851124013868</v>
+        <v>3.302034333369658</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.433653674620584</v>
+        <v>3.772435502983193</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.810424437558775</v>
+        <v>3.136419469362536</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.591630754073714</v>
+        <v>-3.566614773266101</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.641995257526335</v>
+        <v>1.65200164984938</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3397452342405004</v>
+        <v>0.3717172498334839</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.803488234545143</v>
+        <v>3.129483266348904</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240405.xlsx
+++ b/tame_output/ON/bt/strategyON_20240405.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>-3.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>131.9%</t>
+          <t>132.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>500.4%</t>
+          <t>496.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-518.2%</t>
+          <t>-495.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>-40.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3703.5%</t>
+          <t>582.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-211.0%</t>
+          <t>-201.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,32 +1308,32 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.7%</t>
+          <t>-161.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-186.8%</t>
+          <t>-165.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,22 +1466,22 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,22 +1491,22 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-133.1%</t>
+          <t>-102.8%</t>
         </is>
       </c>
     </row>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.401762403767835</v>
+        <v>-5.426778384575448</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9563630751022001</v>
+        <v>0.9463566827791547</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8923256160783768</v>
+        <v>-0.9242976316713598</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.582029091276056</v>
+        <v>2.562845881920266</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.399335339239117</v>
+        <v>-5.424351320046729</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9565884159195188</v>
+        <v>0.9465820235964735</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.8926583978855285</v>
+        <v>-0.9246304134785115</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.581083937197596</v>
+        <v>2.561900727841806</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.807924116419795</v>
+        <v>-5.832940097227407</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7919144490620065</v>
+        <v>0.7819080567389616</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.301247175066207</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.334692214903948</v>
+        <v>2.315509005548158</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.220906600560888</v>
+        <v>-6.245922581368501</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6219068878770297</v>
+        <v>0.6119004955539844</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.301247175066207</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.329877647375409</v>
+        <v>2.310694438019619</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.637298474847886</v>
+        <v>-6.662314455655499</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.453344188771108</v>
+        <v>0.4433377964480627</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.301247175066207</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.327871697984286</v>
+        <v>2.308688488628496</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.01397548537773</v>
+        <v>-7.038991466185343</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3129320752278493</v>
+        <v>0.3029256829048039</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.301247175066207</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.338130388652965</v>
+        <v>2.318947179297175</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.027690349702842</v>
+        <v>-7.052706330510454</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3035456946434998</v>
+        <v>0.2935393023204549</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.301247175066207</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.33422995379866</v>
+        <v>2.31504674444287</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.340515148947821</v>
+        <v>-7.365531129755434</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.1768206950005089</v>
+        <v>0.166814302677464</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.301247175066207</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.332634873853661</v>
+        <v>2.313451664497871</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.345328187413158</v>
+        <v>-7.370344168220771</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1786744555435824</v>
+        <v>0.1686680632205371</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.302793809768993</v>
+        <v>-1.334765825361976</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.335485868961197</v>
+        <v>2.316302659605408</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.778677295523394</v>
+        <v>-7.803693276331007</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.001308507765084954</v>
+        <v>-0.008697884557960389</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.302793809768993</v>
+        <v>-1.334765825361976</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.331459564426795</v>
+        <v>2.312276355071005</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.161678684266025</v>
+        <v>-8.186694665073638</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1519941490535519</v>
+        <v>-0.1620005413765968</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.302793809768993</v>
+        <v>-1.334765825361976</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.331357463105211</v>
+        <v>2.312174253749421</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.536664010437303</v>
+        <v>-8.561679991244915</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.2994167635506324</v>
+        <v>-0.3094231558736777</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.67777913594027</v>
+        <v>-1.709751151533253</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.108937783373874</v>
+        <v>2.089754574018084</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.896194332941304</v>
+        <v>-8.921210313748917</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.4378785892541828</v>
+        <v>-0.4478849815772281</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.67777913594027</v>
+        <v>-1.709751151533253</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.114288086671924</v>
+        <v>2.095104877316134</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.222594361606317</v>
+        <v>-9.24761034241393</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5605225807630108</v>
+        <v>-0.5705289730860557</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.004179164605283</v>
+        <v>-2.036151180198266</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.926364089430094</v>
+        <v>1.907180880074304</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.216118214812758</v>
+        <v>-9.24113419562037</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5548903714238178</v>
+        <v>-0.5648967637468632</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.997703017811723</v>
+        <v>-2.029675033404706</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.933291528127999</v>
+        <v>1.914108318772209</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.212427289856347</v>
+        <v>-9.23744327066396</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.5534140014412539</v>
+        <v>-0.5634203937642988</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.997703017811723</v>
+        <v>-2.029675033404706</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.933291528127999</v>
+        <v>1.914108318772209</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.416685465186211</v>
+        <v>-9.441701445993823</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.6296040744545568</v>
+        <v>-0.6396104667776017</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.125341962425712</v>
+        <v>-2.157313978018695</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.862221358478248</v>
+        <v>1.843038149122458</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.577324491674576</v>
+        <v>-9.602340472482188</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.6893771305654668</v>
+        <v>-0.6993835228885117</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.240075435428108</v>
+        <v>-2.272047451021091</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.797863829161247</v>
+        <v>1.778680619805457</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.503854660007127</v>
+        <v>-9.528870640814739</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6446174964050662</v>
+        <v>-0.6546238887281111</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.166605603760659</v>
+        <v>-2.198577619353642</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.857317429655137</v>
+        <v>1.838134220299347</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.67897907739367</v>
+        <v>-9.703995058201283</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7001120426121665</v>
+        <v>-0.7101184349352119</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.341730021147203</v>
+        <v>-2.373702036740186</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.766797999970727</v>
+        <v>1.747614790614937</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.91343117140816</v>
+        <v>-9.938447152215772</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8011120451195586</v>
+        <v>-0.8111184374426035</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.341730021147203</v>
+        <v>-2.373702036740186</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.759578835069131</v>
+        <v>1.740395625713341</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.2012350159454</v>
+        <v>-10.22625099675301</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9229057737084303</v>
+        <v>-0.9329121660314752</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.629533865684441</v>
+        <v>-2.661505881277424</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.580224337572812</v>
+        <v>1.561041128217022</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.43105946310922</v>
+        <v>-10.45607544391684</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.013719762735404</v>
+        <v>-1.023726155058449</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.792181402754602</v>
+        <v>-2.824153418347585</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.483751605169272</v>
+        <v>1.464568395813482</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.66308838284549</v>
+        <v>-10.6881043636531</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.103837602000794</v>
+        <v>-1.113843994323839</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.854194099943025</v>
+        <v>-2.886166115536008</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.449237715485333</v>
+        <v>1.430054506129543</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.61107286887667</v>
+        <v>-10.63608884968428</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.079041060726868</v>
+        <v>-1.089047453049913</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.854194099943025</v>
+        <v>-2.886166115536008</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.453228051171734</v>
+        <v>1.434044841815944</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.75274471060079</v>
+        <v>-10.7777606914084</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.137185024315258</v>
+        <v>-1.147191416638303</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.854194099943025</v>
+        <v>-2.886166115536008</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.451752824272992</v>
+        <v>1.432569614917202</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.85165145106007</v>
+        <v>-10.87666743186768</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.161694310334096</v>
+        <v>-1.17170070265714</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.9531008404023</v>
+        <v>-2.985072855995284</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.407462190162299</v>
+        <v>1.388278980806509</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.65249934382297</v>
+        <v>-10.67751532463058</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.095084601085939</v>
+        <v>-1.105090993408984</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.787778314452487</v>
+        <v>-2.81975033004547</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.493604572085504</v>
+        <v>1.474421362729714</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.42665419110356</v>
+        <v>-10.45167017191117</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9951674669619659</v>
+        <v>-1.005173859285012</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.745851638865323</v>
+        <v>-2.777823654458307</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.528339650474011</v>
+        <v>1.509156441118221</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.14037937878086</v>
+        <v>-10.16539535958848</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8795183974768297</v>
+        <v>-0.8895247897998746</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.745851638865323</v>
+        <v>-2.777823654458307</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.52947879503007</v>
+        <v>1.51029558567428</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.19327466682515</v>
+        <v>-10.21829064763276</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8980427385324363</v>
+        <v>-0.9080491308554812</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.740896292776877</v>
+        <v>-2.772868308369861</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.535085776845245</v>
+        <v>1.515902567489455</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.909365935896401</v>
+        <v>-9.934381916704014</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.7787455419223002</v>
+        <v>-0.7887519342453455</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.740896292776877</v>
+        <v>-2.772868308369861</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.540819481083882</v>
+        <v>1.521636271728092</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.66237868570345</v>
+        <v>-9.687394666511063</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6896879042389847</v>
+        <v>-0.6996942965620301</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.493909042583925</v>
+        <v>-2.525881058176909</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.679274568805788</v>
+        <v>1.660091359449998</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.39854181849938</v>
+        <v>-9.423557799306993</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5940366386702647</v>
+        <v>-0.6040430309933096</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.493909042583925</v>
+        <v>-2.525881058176909</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.66939108749288</v>
+        <v>1.65020787813709</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.131300017630982</v>
+        <v>-9.409359240279908</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.488974478822279</v>
+        <v>-0.6001981678818495</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.493909042583925</v>
+        <v>-2.525881058176909</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.667556526993506</v>
+        <v>1.648373317637716</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.855490854230498</v>
+        <v>-9.133550076879423</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.378951128435546</v>
+        <v>-0.4901748174951162</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.404889734305192</v>
+        <v>-2.436861749898175</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.720667796987286</v>
+        <v>1.701484587631496</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.586423266463518</v>
+        <v>-8.864482489112444</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2706555871832603</v>
+        <v>-0.3818792762428309</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.135822146538212</v>
+        <v>-2.167794162131196</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.882776855792967</v>
+        <v>1.863593646437177</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.322363328140721</v>
+        <v>-8.600422550789647</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1782919280158941</v>
+        <v>-0.2895156170754642</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.871762208215416</v>
+        <v>-1.9037342238084</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.027952502624892</v>
+        <v>2.008769293269102</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.615283704635883</v>
+        <v>-7.893342927284809</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1017528877257403</v>
+        <v>-0.009470801333829826</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.871762208215416</v>
+        <v>-1.9037342238084</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.025165468964591</v>
+        <v>2.005982259608801</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.365642674649931</v>
+        <v>-7.643701897298857</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2019529236079625</v>
+        <v>0.09072923454839232</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.622121178229464</v>
+        <v>-1.654093193822448</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.175293710844004</v>
+        <v>2.156110501488214</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.111100775308856</v>
+        <v>-7.389159997957782</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3031365045651495</v>
+        <v>0.1919128155055794</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.367579278888389</v>
+        <v>-1.399551294481372</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.327385671669406</v>
+        <v>2.308202462313616</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.877619553079257</v>
+        <v>-7.155678775728183</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4044534222948415</v>
+        <v>0.2932297332352709</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.13409805665879</v>
+        <v>-1.166070072251774</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.475398833845018</v>
+        <v>2.456215624489228</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.697911022935385</v>
+        <v>-6.97597024558431</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4734446240394314</v>
+        <v>0.3622209349798609</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.076926552496094</v>
+        <v>-1.108898568089078</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.506809526029676</v>
+        <v>2.487626316673886</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.565635549304498</v>
+        <v>-6.843694771953424</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5217223002388129</v>
+        <v>0.4104986111792424</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9446510788652076</v>
+        <v>-0.9766230944581911</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.581542296955235</v>
+        <v>2.562359087599445</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.375035874631346</v>
+        <v>-6.653095097280271</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.6007772307957104</v>
+        <v>0.4895535417361403</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7540514041920547</v>
+        <v>-0.7860234197850382</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.698717162446764</v>
+        <v>2.679533953090973</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.126036075947765</v>
+        <v>-6.40409529859669</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.7132834914928017</v>
+        <v>0.6020598024332315</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7540514041920547</v>
+        <v>-0.7860234197850382</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.711623503670422</v>
+        <v>2.692440294314632</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.231626065720869</v>
+        <v>-6.509685288369795</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5430715659843415</v>
+        <v>0.4318478769247709</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.859641393965159</v>
+        <v>-0.8916134095581425</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.520293580207341</v>
+        <v>2.501110370851551</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.250360967839466</v>
+        <v>-6.528420190488392</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5841219470139887</v>
+        <v>0.4728982579544185</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.859641393965159</v>
+        <v>-0.8916134095581425</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.568837922084428</v>
+        <v>2.549654712728637</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.973622793168653</v>
+        <v>-6.251682015817579</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.6981962288683086</v>
+        <v>0.5869725398087384</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6778247328552333</v>
+        <v>-0.7097967484482167</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.681306930736377</v>
+        <v>2.662123721380588</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.846730386733583</v>
+        <v>-6.124789609382509</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.7402392051888587</v>
+        <v>0.6290155161292881</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5509323264201633</v>
+        <v>-0.5829043420131468</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.748728388343941</v>
+        <v>2.729545178988151</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.659142878823657</v>
+        <v>-5.937202101472582</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.8083135962577361</v>
+        <v>0.6970899071981655</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5509323264201633</v>
+        <v>-0.5829043420131468</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.741767776248848</v>
+        <v>2.722584566893058</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.416994485369798</v>
+        <v>-5.695053708018724</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.9196353080204225</v>
+        <v>0.8084116189608519</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5509323264201633</v>
+        <v>-0.5829043420131468</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.756230130629991</v>
+        <v>2.737046921274201</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.35376511360145</v>
+        <v>-5.631824336250376</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.9394591771869569</v>
+        <v>0.8282354881273863</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5509323264201633</v>
+        <v>-0.5829043420131468</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.750762251089186</v>
+        <v>2.731579041733396</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.167277421224444</v>
+        <v>-5.44533664387337</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.011552348148336</v>
+        <v>0.9003286590887658</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3644446340431571</v>
+        <v>-0.3964166496361405</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.860152960525967</v>
+        <v>2.840969751170177</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.146128222321001</v>
+        <v>-5.424187444969927</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.027713005947039</v>
+        <v>0.9164893168874686</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3432954351397137</v>
+        <v>-0.3752674507326972</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.880543458105358</v>
+        <v>2.861360248749568</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.902362780337556</v>
+        <v>-5.180422002986482</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.120999891087467</v>
+        <v>1.009776202027897</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3432954351397137</v>
+        <v>-0.3752674507326972</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.87632416645241</v>
+        <v>2.857140957096619</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.638334713144296</v>
+        <v>-4.916393935793222</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.228735431884788</v>
+        <v>1.117511742825217</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1414300363237602</v>
+        <v>-0.1734020519167436</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.999567719661997</v>
+        <v>2.980384510306207</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.388484319195221</v>
+        <v>-4.666543541844147</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.321417664448119</v>
+        <v>1.210193975388549</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1414300363237602</v>
+        <v>-0.1734020519167436</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.9923097946457</v>
+        <v>2.97312658528991</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.084916830191243</v>
+        <v>-4.362976052840168</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.44644378357036</v>
+        <v>1.335220094510789</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1414300363237602</v>
+        <v>-0.1734020519167436</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.995908918166348</v>
+        <v>2.976725708810558</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.011436921339229</v>
+        <v>-4.289496143988154</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.489163253165719</v>
+        <v>1.377939564106149</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.06795012747174578</v>
+        <v>-0.09992214306472924</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.053324369532111</v>
+        <v>3.034141160176321</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.786403921670406</v>
+        <v>-4.064463144319332</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.578196930649545</v>
+        <v>1.466973241589975</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1570828721970771</v>
+        <v>0.1251108566040936</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.187364646949701</v>
+        <v>3.168181437593911</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.571769544033999</v>
+        <v>-3.849828766682925</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.668745482758425</v>
+        <v>1.557521793698855</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3717172498334839</v>
+        <v>0.3397452342405004</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.320840074585863</v>
+        <v>3.301656865230072</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.566614773266101</v>
+        <v>-3.583228409708573</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.65200164984938</v>
+        <v>1.645356195272391</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3717172498334839</v>
+        <v>0.3397452342405004</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.302034333369658</v>
+        <v>3.282851124013868</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.772435502983193</v>
+        <v>3.435378300342617</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.136419469362536</v>
+        <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.566614773266101</v>
+        <v>-3.337031251129772</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.65200164984938</v>
+        <v>1.745578135328789</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3717172498334839</v>
+        <v>0.5859423928193012</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.129483266348904</v>
+        <v>3.432312495786026</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240405.xlsx
+++ b/tame_output/ON/bt/strategyON_20240405.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.3%</t>
+          <t>133.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-53.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>496.8%</t>
+          <t>496.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-495.3%</t>
+          <t>-529.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>582.9%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-201.7%</t>
+          <t>-215.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.1%</t>
+          <t>-156.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-165.4%</t>
+          <t>-193.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-102.8%</t>
+          <t>-119.8%</t>
         </is>
       </c>
     </row>
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.30471571697091</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.424351320046729</v>
+        <v>-5.756940394523851</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9465820235964735</v>
+        <v>0.8135463938056251</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9246304134785115</v>
+        <v>-1.201069827206096</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.561900727841806</v>
+        <v>2.396037079605255</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330527</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.832940097227407</v>
+        <v>-6.165529171704529</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7819080567389616</v>
+        <v>0.6488724269481128</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.609658604386775</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.315509005548158</v>
+        <v>2.149645357311607</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191743</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.245922581368501</v>
+        <v>-6.578511655845623</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6119004955539844</v>
+        <v>0.4788648657631356</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.609658604386775</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.310694438019619</v>
+        <v>2.144830789783068</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108645</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.662314455655499</v>
+        <v>-6.99490353013262</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4433377964480627</v>
+        <v>0.3103021666572143</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.609658604386775</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.308688488628496</v>
+        <v>2.142824840391945</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.038991466185343</v>
+        <v>-7.371580540662465</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3029256829048039</v>
+        <v>0.1698900531139556</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.609658604386775</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.318947179297175</v>
+        <v>2.153083531060624</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.052706330510454</v>
+        <v>-7.385295404987576</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2935393023204549</v>
+        <v>0.1605036725296061</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.609658604386775</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.31504674444287</v>
+        <v>2.149183096206319</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.365531129755434</v>
+        <v>-7.698120204232556</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.166814302677464</v>
+        <v>0.03377867288661518</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.609658604386775</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.313451664497871</v>
+        <v>2.14758801626132</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.370344168220771</v>
+        <v>-7.702933242697893</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1686680632205371</v>
+        <v>0.03563243342968869</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.611205239089561</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.316302659605408</v>
+        <v>2.150439011368857</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.803693276331007</v>
+        <v>-8.136282350808129</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.008697884557960389</v>
+        <v>-0.1417335143488092</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.611205239089561</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.312276355071005</v>
+        <v>2.146412706834454</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.186694665073638</v>
+        <v>-8.51928373955076</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1620005413765968</v>
+        <v>-0.2950361711674456</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.611205239089561</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.312174253749421</v>
+        <v>2.14631060551287</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.561679991244915</v>
+        <v>-8.894269065722037</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.3094231558736777</v>
+        <v>-0.4424587856645261</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.986190565260838</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.089754574018084</v>
+        <v>1.923890925781533</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.921210313748917</v>
+        <v>-9.253799388226039</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.4478849815772281</v>
+        <v>-0.5809206113680769</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.986190565260838</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.095104877316134</v>
+        <v>1.929241229079584</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.24761034241393</v>
+        <v>-9.580199416891052</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5705289730860557</v>
+        <v>-0.7035646028769045</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.036151180198266</v>
+        <v>-2.312590593925851</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.907180880074304</v>
+        <v>1.741317231837753</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.24113419562037</v>
+        <v>-9.573723270097492</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.5648967637468632</v>
+        <v>-0.697932393537712</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.029675033404706</v>
+        <v>-2.306114447132291</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.914108318772209</v>
+        <v>1.748244670535658</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.23744327066396</v>
+        <v>-9.570032345141081</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.5634203937642988</v>
+        <v>-0.6964560235551476</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.029675033404706</v>
+        <v>-2.306114447132291</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.914108318772209</v>
+        <v>1.748244670535658</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.441701445993823</v>
+        <v>-9.774290520470945</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.6396104667776017</v>
+        <v>-0.7726460965684505</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.157313978018695</v>
+        <v>-2.43375339174628</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.843038149122458</v>
+        <v>1.677174500885907</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.602340472482188</v>
+        <v>-9.93492954695931</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.6993835228885117</v>
+        <v>-0.8324191526793605</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.272047451021091</v>
+        <v>-2.548486864748676</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.778680619805457</v>
+        <v>1.612816971568906</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.528870640814739</v>
+        <v>-9.861459715291861</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.6546238887281111</v>
+        <v>-0.7876595185189599</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.198577619353642</v>
+        <v>-2.475017033081227</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.838134220299347</v>
+        <v>1.672270572062796</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.703995058201283</v>
+        <v>-10.0365841326784</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7101184349352119</v>
+        <v>-0.8431540647260602</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.650141450467771</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.747614790614937</v>
+        <v>1.581751142378386</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.938447152215772</v>
+        <v>-10.27103622669289</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8111184374426035</v>
+        <v>-0.9441540672334523</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.650141450467771</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.740395625713341</v>
+        <v>1.57453197747679</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.22625099675301</v>
+        <v>-10.55884007123013</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9329121660314752</v>
+        <v>-1.065947795822324</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.661505881277424</v>
+        <v>-2.937945295005009</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.561041128217022</v>
+        <v>1.395177479980471</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.45607544391684</v>
+        <v>-10.78866451839396</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.023726155058449</v>
+        <v>-1.156761784849298</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.824153418347585</v>
+        <v>-3.10059283207517</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.464568395813482</v>
+        <v>1.298704747576931</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.6881043636531</v>
+        <v>-11.02069343813022</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.113843994323839</v>
+        <v>-1.246879624114687</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.886166115536008</v>
+        <v>-3.162605529263593</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.430054506129543</v>
+        <v>1.264190857892992</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63608884968428</v>
+        <v>-10.96867792416141</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.089047453049913</v>
+        <v>-1.222083082840761</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.886166115536008</v>
+        <v>-3.162605529263593</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.434044841815944</v>
+        <v>1.268181193579393</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.7777606914084</v>
+        <v>-11.11034976588553</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.147191416638303</v>
+        <v>-1.280227046429151</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.886166115536008</v>
+        <v>-3.162605529263593</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.432569614917202</v>
+        <v>1.266705966680651</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.87666743186768</v>
+        <v>-11.2092565063448</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.17170070265714</v>
+        <v>-1.30473633244799</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.985072855995284</v>
+        <v>-3.261512269722868</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.388278980806509</v>
+        <v>1.222415332569958</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.67751532463058</v>
+        <v>-11.0101043991077</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.105090993408984</v>
+        <v>-1.238126623199833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.81975033004547</v>
+        <v>-3.096189743773055</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.474421362729714</v>
+        <v>1.308557714493163</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.45167017191117</v>
+        <v>-10.78425924638829</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.005173859285012</v>
+        <v>-1.138209489075859</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.777823654458307</v>
+        <v>-3.054263068185891</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.509156441118221</v>
+        <v>1.34329279288167</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.16539535958848</v>
+        <v>-10.4979844340656</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8895247897998746</v>
+        <v>-1.022560419590722</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.777823654458307</v>
+        <v>-3.054263068185891</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.51029558567428</v>
+        <v>1.344431937437729</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.21829064763276</v>
+        <v>-10.55087972210988</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9080491308554812</v>
+        <v>-1.04108476064633</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.772868308369861</v>
+        <v>-3.049307722097445</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.515902567489455</v>
+        <v>1.350038919252905</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.934381916704014</v>
+        <v>-10.26697099118113</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.7887519342453455</v>
+        <v>-0.921787564036193</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.772868308369861</v>
+        <v>-3.049307722097445</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.521636271728092</v>
+        <v>1.355772623491541</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.687394666511063</v>
+        <v>-10.01998374098818</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6996942965620301</v>
+        <v>-0.8327299263528776</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.802320471904493</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.660091359449998</v>
+        <v>1.494227711213447</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.423557799306993</v>
+        <v>-9.756146873784113</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.6040430309933096</v>
+        <v>-0.7370786607841575</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.802320471904493</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.65020787813709</v>
+        <v>1.484344229900539</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.409359240279908</v>
+        <v>-9.741948314757028</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6001981678818495</v>
+        <v>-0.7332337976726975</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.802320471904493</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.648373317637716</v>
+        <v>1.482509669401166</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.133550076879423</v>
+        <v>-9.466139151356543</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4901748174951162</v>
+        <v>-0.6232104472859645</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.436861749898175</v>
+        <v>-2.71330116362576</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.701484587631496</v>
+        <v>1.535620939394945</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.864482489112444</v>
+        <v>-9.197071563589564</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3818792762428309</v>
+        <v>-0.5149149060336788</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.167794162131196</v>
+        <v>-2.44423357585878</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.863593646437177</v>
+        <v>1.697729998200626</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.600422550789647</v>
+        <v>-8.933011625266767</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2895156170754642</v>
+        <v>-0.4225512468663122</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.9037342238084</v>
+        <v>-2.180173637535984</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.008769293269102</v>
+        <v>1.842905645032552</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.893342927284809</v>
+        <v>-8.22593200176193</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.009470801333829826</v>
+        <v>-0.1425064311246782</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.9037342238084</v>
+        <v>-2.180173637535984</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.005982259608801</v>
+        <v>1.840118611372251</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.643701897298857</v>
+        <v>-7.976290971775978</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.09072923454839232</v>
+        <v>-0.04230639524245605</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.654093193822448</v>
+        <v>-1.930532607550033</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.156110501488214</v>
+        <v>1.990246853251663</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.389159997957782</v>
+        <v>-7.721749072434902</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1919128155055794</v>
+        <v>0.05887718571473144</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.399551294481372</v>
+        <v>-1.675990708208957</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.308202462313616</v>
+        <v>2.142338814077065</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.155678775728183</v>
+        <v>-7.488267850205303</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2932297332352709</v>
+        <v>0.160194103444423</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.166070072251774</v>
+        <v>-1.442509485979359</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.456215624489228</v>
+        <v>2.290351976252677</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.97597024558431</v>
+        <v>-7.30855932006143</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3622209349798609</v>
+        <v>0.2291853051890129</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.108898568089078</v>
+        <v>-1.385337981816662</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.487626316673886</v>
+        <v>2.321762668437335</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.843694771953424</v>
+        <v>-7.176283846430544</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4104986111792424</v>
+        <v>0.2774629813883944</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9766230944581911</v>
+        <v>-1.253062508185776</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.562359087599445</v>
+        <v>2.396495439362894</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.653095097280271</v>
+        <v>-6.985684171757391</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4895535417361403</v>
+        <v>0.3565179119452924</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7860234197850382</v>
+        <v>-1.062462833512623</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.679533953090973</v>
+        <v>2.513670304854423</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.40409529859669</v>
+        <v>-6.73668437307381</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6020598024332315</v>
+        <v>0.4690241726423836</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7860234197850382</v>
+        <v>-1.062462833512623</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.692440294314632</v>
+        <v>2.526576646078082</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.509685288369795</v>
+        <v>-6.842274362846915</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4318478769247709</v>
+        <v>0.298812247133923</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8916134095581425</v>
+        <v>-1.168052823285727</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.501110370851551</v>
+        <v>2.335246722615</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.528420190488392</v>
+        <v>-6.861009264965512</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4728982579544185</v>
+        <v>0.3398626281635706</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8916134095581425</v>
+        <v>-1.168052823285727</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.549654712728637</v>
+        <v>2.383791064492087</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.251682015817579</v>
+        <v>-6.584271090294699</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.5869725398087384</v>
+        <v>0.4539369100178905</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.7097967484482167</v>
+        <v>-0.9862361621758015</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.662123721380588</v>
+        <v>2.496260073144037</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124789609382509</v>
+        <v>-6.457378683859629</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.6290155161292881</v>
+        <v>0.4959798863384401</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.8593437557407315</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.729545178988151</v>
+        <v>2.5636815307516</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.937202101472582</v>
+        <v>-6.269791175949702</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.6970899071981655</v>
+        <v>0.5640542774073176</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.8593437557407315</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.722584566893058</v>
+        <v>2.556720918656507</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.695053708018724</v>
+        <v>-6.027642782495844</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.8084116189608519</v>
+        <v>0.675375989170004</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.8593437557407315</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.737046921274201</v>
+        <v>2.57118327303765</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.631824336250376</v>
+        <v>-5.964413410727496</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.8282354881273863</v>
+        <v>0.6951998583365384</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.8593437557407315</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.731579041733396</v>
+        <v>2.565715393496845</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.44533664387337</v>
+        <v>-5.77792571835049</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.9003286590887658</v>
+        <v>0.7672930292979179</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3964166496361405</v>
+        <v>-0.6728560633637253</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.840969751170177</v>
+        <v>2.675106102933626</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.424187444969927</v>
+        <v>-5.756776519447047</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.9164893168874686</v>
+        <v>0.7834536870966207</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3752674507326972</v>
+        <v>-0.6517068644602819</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.861360248749568</v>
+        <v>2.695496600513018</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.180422002986482</v>
+        <v>-5.513011077463602</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.009776202027897</v>
+        <v>0.8767405722370492</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3752674507326972</v>
+        <v>-0.6517068644602819</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.857140957096619</v>
+        <v>2.691277308860069</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.916393935793222</v>
+        <v>-5.248983010270342</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.117511742825217</v>
+        <v>0.9844761130343693</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.4498414656443284</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.980384510306207</v>
+        <v>2.814520862069656</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.666543541844147</v>
+        <v>-4.999132616321267</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.210193975388549</v>
+        <v>1.077158345597701</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.4498414656443284</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.97312658528991</v>
+        <v>2.807262937053359</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.362976052840168</v>
+        <v>-4.695565127317288</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.335220094510789</v>
+        <v>1.202184464719942</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.4498414656443284</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.976725708810558</v>
+        <v>2.810862060574007</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.289496143988154</v>
+        <v>-4.622085218465275</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.377939564106149</v>
+        <v>1.244903934315301</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.09992214306472924</v>
+        <v>-0.376361556792314</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.034141160176321</v>
+        <v>2.86827751193977</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.064463144319332</v>
+        <v>-4.397052218796452</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.466973241589975</v>
+        <v>1.333937611799127</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1251108566040936</v>
+        <v>-0.1513285571234911</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.168181437593911</v>
+        <v>3.00231778935736</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.849828766682925</v>
+        <v>-4.182417841160045</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.557521793698855</v>
+        <v>1.424486163908007</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3397452342405004</v>
+        <v>0.06330582051291567</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.301656865230072</v>
+        <v>3.135793216993522</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.583228409708573</v>
+        <v>-3.915817484185693</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.645356195272391</v>
+        <v>1.512320565481543</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3397452342405004</v>
+        <v>0.06330582051291567</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.282851124013868</v>
+        <v>3.116987475777317</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.435378300342617</v>
+        <v>3.432594939503291</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-3.337031251129772</v>
+        <v>-3.676032638916368</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.745578135328789</v>
+        <v>1.609977580214151</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.5859423928193012</v>
+        <v>0.3030906657822408</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.432312495786026</v>
+        <v>3.26260145956379</v>
       </c>
     </row>
   </sheetData>
